--- a/artfynd/A 12807-2023 artfynd.xlsx
+++ b/artfynd/A 12807-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12807-2023 artfynd.xlsx
+++ b/artfynd/A 12807-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96512131</v>
+        <v>96535836</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Syd Ramsjön, Vg</t>
+          <t>Syd Ramnsjön, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342290.3643309982</v>
+        <v>342345</v>
       </c>
       <c r="R2" t="n">
-        <v>6376638.685313435</v>
+        <v>6376587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +747,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>delvis självföryngrad granskog med inslag av löv och tall</t>
+          <t>delvis självföryngrad granskog med tall och löv</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -808,12 +785,7 @@
         <v>96512058</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -857,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342269.4634157704</v>
+        <v>342269</v>
       </c>
       <c r="R3" t="n">
-        <v>6376641.647105351</v>
+        <v>6376642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,19 +862,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,6 +894,121 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96512131</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Syd Ramsjön, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>342290</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6376639</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sätila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-10-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>delvis självföryngrad granskog med inslag av löv och tall</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Kuylenstierna</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Kuylenstierna</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
